--- a/00-Administratif/01-ETIQUETTES + NOMBRE  NOTES SEMESTRIELLES/PELE/CONTROLE NOMBRE DE NOTES PELE 4.xlsx
+++ b/00-Administratif/01-ETIQUETTES + NOMBRE  NOTES SEMESTRIELLES/PELE/CONTROLE NOMBRE DE NOTES PELE 4.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29022"/>
   <workbookPr defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="0" documentId="11_6BB03172A6FC0BDB746101660E5A2AFD2DD28B00" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="PELE 4" sheetId="10" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1135,6 +1137,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1">
@@ -1143,15 +1154,6 @@
     <TaxCatchAll xmlns="28ecda99-baeb-4159-826c-8d3ebe501c98" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1390,11 +1392,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F994B24E-E1BC-4294-8270-8C58189F04CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA20DEB-CD3D-4122-BE9E-F407CE793359}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA20DEB-CD3D-4122-BE9E-F407CE793359}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F994B24E-E1BC-4294-8270-8C58189F04CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
